--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$38</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="361">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,33 +431,57 @@
     <t>DiagnosticReport.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:TestedByIndex</t>
+  </si>
+  <si>
+    <t>TestedByIndex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/tested-by-user-index}
+</t>
+  </si>
+  <si>
+    <t>HIV Viral Load Result Tested By</t>
+  </si>
+  <si>
+    <t>The user index for the person who tested the viral load specimen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -465,6 +489,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -550,9 +577,6 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
-    <t>final</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -659,17 +683,13 @@
     <t>DiagnosticReport.code.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1444,12 +1464,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.69140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.37890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1457,7 +1477,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.13671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2415,11 +2435,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2434,17 +2454,15 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -2481,16 +2499,14 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2514,7 +2530,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
@@ -2525,43 +2541,41 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2609,7 +2623,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2618,7 +2632,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -2630,7 +2644,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -2638,14 +2652,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2658,13 +2672,13 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>149</v>
@@ -2725,7 +2739,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2737,31 +2751,31 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2777,22 +2791,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2841,7 +2855,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2856,47 +2870,47 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>168</v>
@@ -2904,9 +2918,11 @@
       <c r="M13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2916,7 +2932,7 @@
         <v>80</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>80</v>
@@ -2931,13 +2947,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -2955,13 +2971,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -2970,58 +2986,58 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3045,13 +3061,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3069,13 +3085,13 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
@@ -3084,35 +3100,35 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
@@ -3124,15 +3140,17 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3157,11 +3175,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3179,13 +3199,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3194,32 +3214,32 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>198</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>89</v>
@@ -3231,16 +3251,16 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3267,13 +3287,11 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3291,10 +3309,10 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>89</v>
@@ -3303,38 +3321,38 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>204</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3346,17 +3364,15 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3393,16 +3409,16 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>210</v>
@@ -3411,13 +3427,13 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -3426,7 +3442,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -3434,14 +3450,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3457,10 +3473,10 @@
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>213</v>
@@ -3469,11 +3485,9 @@
         <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3509,19 +3523,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3533,16 +3547,16 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -3550,10 +3564,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3564,7 +3578,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>80</v>
@@ -3576,19 +3590,19 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3598,7 +3612,7 @@
         <v>80</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>80</v>
@@ -3637,13 +3651,13 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
@@ -3655,10 +3669,10 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -3666,18 +3680,18 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3692,17 +3706,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3712,7 +3728,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -3751,7 +3767,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3766,28 +3782,28 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3806,19 +3822,17 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3867,7 +3881,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3882,32 +3896,32 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -3922,19 +3936,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -3983,7 +3997,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3998,28 +4012,28 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4038,19 +4052,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4099,7 +4113,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4114,35 +4128,35 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4154,19 +4168,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4215,13 +4229,13 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4230,32 +4244,32 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -4270,19 +4284,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4331,7 +4345,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4346,16 +4360,16 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4367,11 +4381,11 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -4383,10 +4397,10 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>290</v>
@@ -4398,7 +4412,7 @@
         <v>292</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4462,35 +4476,35 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -4502,19 +4516,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4563,7 +4577,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4581,10 +4595,10 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4592,21 +4606,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4618,18 +4632,20 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
@@ -4677,7 +4693,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4695,7 +4711,7 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>309</v>
@@ -4713,7 +4729,7 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4729,21 +4745,21 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4809,10 +4825,10 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4820,21 +4836,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -4843,19 +4859,21 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>200</v>
+        <v>318</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>201</v>
+        <v>319</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>202</v>
+        <v>320</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4903,28 +4921,28 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4932,21 +4950,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -4958,17 +4976,15 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5023,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5038,7 +5054,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5046,14 +5062,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>148</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5066,26 +5082,24 @@
         <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>213</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>214</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5133,7 +5147,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>323</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5154,7 +5168,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>132</v>
+        <v>211</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5162,45 +5176,45 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>327</v>
+        <v>151</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>328</v>
+        <v>152</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5249,19 +5263,19 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5270,7 +5284,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>132</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5289,7 +5303,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -5301,19 +5315,23 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5364,7 +5382,7 @@
         <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>89</v>
@@ -5382,7 +5400,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5390,44 +5408,42 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>200</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5475,10 +5491,10 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -5493,10 +5509,10 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5504,24 +5520,24 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -5530,7 +5546,7 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>343</v>
@@ -5539,7 +5555,9 @@
         <v>344</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5563,13 +5581,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>345</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5587,13 +5605,13 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
@@ -5605,7 +5623,7 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>347</v>
@@ -5642,20 +5660,16 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5679,13 +5693,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -5721,17 +5735,133 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="B38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN37">
+  <autoFilter ref="A1:AN38">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5741,7 +5871,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI36">
+  <conditionalFormatting sqref="A2:AI37">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$46</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="390">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -240,13 +240,13 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t>Report
@@ -269,7 +269,7 @@
     <t>A Diagnostic report - a combination of request information, atomic results, images, interpretation, as well as formatted reports</t>
   </si>
   <si>
-    <t>The findings and interpretation of diagnostic  tests performed on patients, groups of patients, devices, and locations, and/or specimens derived from these. The report includes clinical context such as requesting and provider information, and some mix of atomic results, images, textual and coded interpretations, and formatted representation of diagnostic reports.</t>
+    <t>The findings and interpretation of diagnostic tests performed on patients, groups of patients, products, substances, devices, and locations, and/or specimens derived from these. The report includes clinical context such as requesting provider information, and some mix of atomic results, images, textual and coded interpretations, and formatted representation of diagnostic reports. The report also includes non-clinical context such as batch analysis and stability reporting of products and substances.</t>
   </si>
   <si>
     <t>This is intended to capture a single report and is not suitable for use in displaying summary information that covers multiple reports.  For example, this resource has not been designed for laboratory cumulative reporting formats nor detailed structured reports for sequencing.</t>
@@ -278,10 +278,13 @@
     <t>Event</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>ORU -&gt; OBR</t>
   </si>
   <si>
-    <t>Observation[classCode=OBS, moodCode=EVN]</t>
+    <t>Entity, Role, or Act,Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
     <t>DiagnosticReport.id</t>
@@ -303,7 +306,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -342,7 +345,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -364,13 +367,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -393,10 +396,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -416,13 +423,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -471,261 +482,258 @@
     <t>The user index for the person who tested the viral load specimen.</t>
   </si>
   <si>
+    <t>DiagnosticReport.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier</t>
+  </si>
+  <si>
+    <t>ReportID
+Filler IDPlacer ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business identifier for report</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this report by the performer or other systems.</t>
+  </si>
+  <si>
+    <t>Usually assigned by the Information System of the diagnostic service provider (filler id).</t>
+  </si>
+  <si>
+    <t>Need to know what identifier to use when making queries about this report from the source laboratory, and for linking to the report outside FHIR context.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>OBR-51/ for globally unique filler ID  - OBR-3 , For non-globally unique filler-id the flller/placer number must be combined with the universal service Id -  OBR-2(if present)+OBR-3+OBR-4</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ServiceRequest)
+</t>
+  </si>
+  <si>
+    <t>What was requested</t>
+  </si>
+  <si>
+    <t>Details concerning a service requested.</t>
+  </si>
+  <si>
+    <t>Note: Usually there is one test request for each result, however in some circumstances multiple test requests may be represented using a single test result resource. Note that there are also cases where one request leads to multiple reports.</t>
+  </si>
+  <si>
+    <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>ORC? OBR-2/3?</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.status</t>
+  </si>
+  <si>
+    <t>registered | partial | preliminary | modified | final | amended | corrected | appended | cancelled | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>The status of the diagnostic report.</t>
+  </si>
+  <si>
+    <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|5.0.0</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>OBR-25 (not 1:1 mapping)</t>
+  </si>
+  <si>
+    <t>statusCode  Note: final and amended are distinguished by whether observation is the subject of a ControlAct event of type "revise"</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category</t>
+  </si>
+  <si>
+    <t>Department
+Sub-departmentServiceDiscipline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Service category</t>
+  </si>
+  <si>
+    <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
+  </si>
+  <si>
+    <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>HL7 V2 table 0074</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type
+</t>
+  </si>
+  <si>
+    <t>Name/Code for this diagnostic report</t>
+  </si>
+  <si>
+    <t>A code or name that describes this diagnostic report.</t>
+  </si>
+  <si>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>OBR-4 (HL7 V2 doesn't provide an easy way to indicate both the ordered test and the performed panel)</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.identifier</t>
-  </si>
-  <si>
-    <t>ReportID
-Filler IDPlacer ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
-    <t>Business identifier for report</t>
-  </si>
-  <si>
-    <t>Identifiers assigned to this report by the performer or other systems.</t>
-  </si>
-  <si>
-    <t>Usually assigned by the Information System of the diagnostic service provider (filler id).</t>
-  </si>
-  <si>
-    <t>Need to know what identifier to use when making queries about this report from the source laboratory, and for linking to the report outside FHIR context.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>OBR-51/ for globally unique filler ID  - OBR-3 , For non-globally unique filler-id the flller/placer number must be combined with the universal service Id -  OBR-2(if present)+OBR-3+OBR-4</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
-</t>
-  </si>
-  <si>
-    <t>What was requested</t>
-  </si>
-  <si>
-    <t>Details concerning a service requested.</t>
-  </si>
-  <si>
-    <t>Note: Usually there is one test request for each result, however in some circumstances multiple test requests may be represented using a single test result resource. Note that there are also cases where one request leads to multiple reports.</t>
-  </si>
-  <si>
-    <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>ORC? OBR-2/3?</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.status</t>
-  </si>
-  <si>
-    <t>registered | partial | preliminary | final +</t>
-  </si>
-  <si>
-    <t>The status of the diagnostic report.</t>
-  </si>
-  <si>
-    <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>OBR-25 (not 1:1 mapping)</t>
-  </si>
-  <si>
-    <t>statusCode  Note: final and amended are distinguished by whether observation is the subject of a ControlAct event of type "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category</t>
-  </si>
-  <si>
-    <t>Department
-Sub-departmentServiceDiscipline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Service category</t>
-  </si>
-  <si>
-    <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
-  </si>
-  <si>
-    <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type
-</t>
-  </si>
-  <si>
-    <t>Name/Code for this diagnostic report</t>
-  </si>
-  <si>
-    <t>A code or name that describes this diagnostic report.</t>
-  </si>
-  <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>OBR-4 (HL7 v2 doesn't provide an easy way to indicate both the ordered test and the performed panel)</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.id</t>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.text</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -757,7 +765,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Practitioner|Medication|Substance|BiologicallyDerivedProduct)
 </t>
   </si>
   <si>
@@ -773,13 +781,13 @@
     <t>Event.subject</t>
   </si>
   <si>
-    <t>PID-3 (no HL7 v2 mapping for Group or Device)</t>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
+    <t>PID-3 (no HL7 V2 mapping for Group or Device)</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
   </si>
   <si>
     <t>DiagnosticReport.encounter</t>
@@ -808,13 +816,13 @@
     <t>Event.encounter</t>
   </si>
   <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
     <t>PV1-19</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
   </si>
   <si>
     <t>DiagnosticReport.effective[x]</t>
@@ -843,13 +851,13 @@
     <t>Event.occurrence[x]</t>
   </si>
   <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
     <t>OBR-7</t>
   </si>
   <si>
     <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
   </si>
   <si>
     <t>DiagnosticReport.issued</t>
@@ -875,13 +883,13 @@
     <t>Clinicians need to be able to check the date that the report was released.</t>
   </si>
   <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
     <t>OBR-22</t>
   </si>
   <si>
     <t>participation[typeCode=VRF or AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
   </si>
   <si>
     <t>DiagnosticReport.performer</t>
@@ -910,13 +918,13 @@
     <t>Event.performer.actor</t>
   </si>
   <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
     <t>PRT-8 (where this PRT-4-Participation = "PO")</t>
   </si>
   <si>
     <t>.participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -974,7 +982,7 @@
     <t>Observations</t>
   </si>
   <si>
-    <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
+    <t>[Observations](http://hl7.org/fhir/R5/observation.html)  that are part of this diagnostic report.</t>
   </si>
   <si>
     <t>Observations can contain observations.</t>
@@ -983,29 +991,113 @@
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
   </si>
   <si>
+    <t xml:space="preserve">dgr-1
+</t>
+  </si>
+  <si>
     <t>OBXs</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=COMP].target</t>
   </si>
   <si>
-    <t>DiagnosticReport.imagingStudy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t>DiagnosticReport.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
 </t>
   </si>
   <si>
-    <t>Reference to full details of imaging associated with the diagnostic report</t>
-  </si>
-  <si>
-    <t>One or more links to full details of any imaging performed during the diagnostic investigation. Typically, this is imaging performed by DICOM enabled modalities, but this is not required. A fully enabled PACS viewer can use this information to provide views of the source images.</t>
-  </si>
-  <si>
-    <t>ImagingStudy and the image element are somewhat overlapping - typically, the list of image references in the image element will also be found in one of the imaging study resources. However, each caters to different types of displays for different types of purposes. Neither, either, or both may be provided.</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=COMP].target[classsCode=DGIMG, moodCode=EVN]</t>
+    <t>Comments about the diagnostic report</t>
+  </si>
+  <si>
+    <t>Comments about the diagnostic report.</t>
+  </si>
+  <si>
+    <t>May include general statements about the diagnostic report, or statements about significant, unexpected or unreliable results values contained within the diagnostic report, or information about its source when relevant to its interpretation.</t>
+  </si>
+  <si>
+    <t>Need to be able to provide free text additional information.</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(GenomicStudy|ImagingStudy)
+</t>
+  </si>
+  <si>
+    <t>Reference to full details of an analysis associated with the diagnostic report</t>
+  </si>
+  <si>
+    <t>One or more links to full details of any study performed during the diagnostic investigation. An ImagingStudy might comprise a set of radiologic images obtained via a procedure that are analyzed as a group. Typically, this is imaging performed by DICOM enabled modalities, but this is not required. A fully enabled PACS viewer can use this information to provide views of the source images. A GenomicStudy might comprise one or more analyses, each serving a specific purpose. These analyses may vary in method (e.g., karyotyping, CNV, or SNV detection), performer, software, devices used, or regions targeted.</t>
+  </si>
+  <si>
+    <t>For laboratory-type studies like GenomeStudy, type resources will be used for tracking additional metadata and workflow aspects of complex studies. ImagingStudy and the media element are somewhat overlapping - typically, the list of image references in the media element will also be found in one of the imaging study resources. However, each caters to different types of displays for different types of purposes. Neither, either, or both may be provided.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.supportingInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Additional information supporting the diagnostic report</t>
+  </si>
+  <si>
+    <t>This backbone element contains supporting information that was used in the creation of the report not included in the results already included in the report.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.supportingInfo.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.supportingInfo.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.supportingInfo.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.supportingInfo.type</t>
+  </si>
+  <si>
+    <t>Supporting information role code</t>
+  </si>
+  <si>
+    <t>The code value for the role of the supporting information in the diagnostic report.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0936</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.supportingInfo.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Procedure|Observation|DiagnosticReport|Citation)
+</t>
+  </si>
+  <si>
+    <t>Supporting information reference</t>
+  </si>
+  <si>
+    <t>The reference for the supporting information in the diagnostic report.</t>
   </si>
   <si>
     <t>DiagnosticReport.media</t>
@@ -1015,77 +1107,75 @@
 SlidesScans</t>
   </si>
   <si>
-    <t xml:space="preserve">BackboneElement
+    <t>Key images or data associated with this report</t>
+  </si>
+  <si>
+    <t>A list of key images or data associated with this report. The images or data are generally created during the diagnostic process, and may be directly of the patient, or of treated specimens (i.e. slides of interest).</t>
+  </si>
+  <si>
+    <t>Many diagnostic services include images or data in the report as part of their service.</t>
+  </si>
+  <si>
+    <t>OBX?</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.media.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.media.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.media.modifierExtension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.media.comment</t>
+  </si>
+  <si>
+    <t>Comment about the image or data (e.g. explanation)</t>
+  </si>
+  <si>
+    <t>A comment about the image or data. Typically, this is used to provide an explanation for why the image or data is included, or to draw the viewer's attention to important features.</t>
+  </si>
+  <si>
+    <t>The comment should be displayed with the image or data. It would be common for the report to include additional discussion of the image or data contents or in other sections such as the conclusion.</t>
+  </si>
+  <si>
+    <t>The provider of the report should make a comment about each image or data included in the report.</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.media.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference)
 </t>
   </si>
   <si>
-    <t>Key images associated with this report</t>
-  </si>
-  <si>
-    <t>A list of key images associated with this report. The images are generally created during the diagnostic process, and may be directly of the patient, or of treated specimens (i.e. slides of interest).</t>
-  </si>
-  <si>
-    <t>Many diagnostic services include images in the report as part of their service.</t>
-  </si>
-  <si>
-    <t>OBX?</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.media.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.media.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.media.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.media.comment</t>
-  </si>
-  <si>
-    <t>Comment about the image (e.g. explanation)</t>
-  </si>
-  <si>
-    <t>A comment about the image. Typically, this is used to provide an explanation for why the image is included, or to draw the viewer's attention to important features.</t>
-  </si>
-  <si>
-    <t>The comment should be displayed with the image. It would be common for the report to include additional discussion of the image contents in other sections such as the conclusion.</t>
-  </si>
-  <si>
-    <t>The provider of the report should make a comment about each image included in the report.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.media.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Media)
+    <t>Reference to the image or data source</t>
+  </si>
+  <si>
+    <t>Reference to the image or data source.</t>
+  </si>
+  <si>
+    <t>.value.reference</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Composition)
 </t>
   </si>
   <si>
-    <t>Reference to the image source</t>
-  </si>
-  <si>
-    <t>Reference to the image source.</t>
-  </si>
-  <si>
-    <t>.value.reference</t>
+    <t>Reference to a Composition resource for the DiagnosticReport structure</t>
+  </si>
+  <si>
+    <t>Reference to a Composition resource instance that provides structure for organizing the contents of the DiagnosticReport.</t>
+  </si>
+  <si>
+    <t>The Composition provides structure to the content of the DiagnosticReport (and only contains contents referenced in the DiagnosticReport) - e.g., to order the sections of an anatomic pathology structured report.</t>
   </si>
   <si>
     <t>DiagnosticReport.conclusion</t>
@@ -1095,6 +1185,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
     <t>Clinical conclusion (interpretation) of test results</t>
   </si>
   <si>
@@ -1119,7 +1213,7 @@
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
   </si>
   <si>
-    <t>Diagnosis codes provided as adjuncts to the report.</t>
+    <t>SNOMED CT Clinical Findings</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
@@ -1296,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1383,77 +1477,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -1464,11 +1566,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN38"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.69140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.01171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.01171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1477,7 +1579,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.89453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="109.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1491,21 +1593,21 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="48.453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="76.1015625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="53.5625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.23046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="121.93359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1741,15 +1843,15 @@
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1760,7 +1862,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>80</v>
@@ -1769,19 +1871,19 @@
         <v>80</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1831,13 +1933,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -1860,10 +1962,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1874,7 +1976,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>80</v>
@@ -1883,16 +1985,16 @@
         <v>80</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1943,19 +2045,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -1972,10 +2074,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1986,28 +2088,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2057,19 +2159,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2086,10 +2188,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2100,7 +2202,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2112,16 +2214,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2147,13 +2249,13 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>80</v>
@@ -2171,19 +2273,19 @@
         <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2200,21 +2302,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -2226,16 +2328,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2285,19 +2387,19 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
@@ -2306,22 +2408,22 @@
         <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>80</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2340,16 +2442,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2399,7 +2501,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2408,7 +2510,7 @@
         <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>80</v>
@@ -2420,18 +2522,18 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2439,7 +2541,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2454,13 +2556,13 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2499,17 +2601,17 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2521,7 +2623,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2538,26 +2640,26 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>80</v>
@@ -2566,13 +2668,13 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2623,7 +2725,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2632,10 +2734,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -2652,14 +2754,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2672,25 +2774,25 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -2739,7 +2841,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2751,7 +2853,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -2760,22 +2862,22 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2791,22 +2893,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2855,7 +2957,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2867,31 +2969,31 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2910,19 +3012,19 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2971,7 +3073,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2983,27 +3085,27 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3011,32 +3113,32 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3061,67 +3163,67 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3137,19 +3239,19 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3175,13 +3277,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3199,7 +3301,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3211,38 +3313,38 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3251,16 +3353,16 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3287,11 +3389,11 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3309,39 +3411,39 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3352,7 +3454,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3364,7 +3466,7 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>208</v>
@@ -3427,10 +3529,10 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>80</v>
@@ -3442,22 +3544,22 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>80</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3476,16 +3578,16 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3523,19 +3625,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3547,7 +3649,7 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -3556,18 +3658,18 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>80</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3587,22 +3689,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3651,7 +3753,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3663,27 +3765,27 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>80</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3694,7 +3796,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -3703,22 +3805,22 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3728,7 +3830,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -3767,50 +3869,50 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>80</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -3819,20 +3921,20 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3881,50 +3983,50 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -3933,22 +4035,22 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -3997,50 +4099,50 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -4049,22 +4151,22 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4113,50 +4215,50 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4165,22 +4267,22 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4229,74 +4331,74 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4345,7 +4447,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4357,35 +4459,35 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -4397,22 +4499,22 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4461,7 +4563,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4473,27 +4575,27 @@
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4516,19 +4618,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4577,7 +4679,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4589,41 +4691,41 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>80</v>
@@ -4632,19 +4734,19 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4693,7 +4795,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4702,30 +4804,30 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4739,7 +4841,7 @@
         <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>80</v>
@@ -4748,18 +4850,20 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4807,7 +4911,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4819,7 +4923,7 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -4828,22 +4932,22 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4859,21 +4963,21 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4921,7 +5025,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4933,16 +5037,16 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>309</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4950,10 +5054,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4964,7 +5068,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -4976,13 +5080,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>207</v>
+        <v>326</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>327</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>209</v>
+        <v>328</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5033,19 +5137,19 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5054,7 +5158,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5062,21 +5166,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5088,17 +5192,15 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5147,19 +5249,19 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5168,22 +5270,22 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>326</v>
+        <v>150</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5196,26 +5298,24 @@
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>214</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5263,7 +5363,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5275,7 +5375,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5284,53 +5384,53 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>80</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
+        <v>153</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>334</v>
+        <v>154</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5379,19 +5479,19 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5400,10 +5500,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -5419,10 +5519,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -5431,16 +5531,16 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5467,13 +5567,13 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -5494,16 +5594,16 @@
         <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -5512,7 +5612,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5520,24 +5620,24 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -5546,18 +5646,16 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>207</v>
+        <v>341</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5605,28 +5703,28 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5634,14 +5732,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5657,19 +5755,21 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>326</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5693,13 +5793,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -5717,7 +5817,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5729,27 +5829,27 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5760,7 +5860,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -5772,20 +5872,16 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>355</v>
+        <v>228</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>208</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5833,35 +5929,949 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>80</v>
+      <c r="H45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN38">
+  <autoFilter ref="A1:AN46">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5871,7 +6881,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI37">
+  <conditionalFormatting sqref="A2:AI45">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
